--- a/reports/pdf_change_20260703.xlsx
+++ b/reports/pdf_change_20260703.xlsx
@@ -575,7 +575,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 6,036억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 6종목  /  매도 6종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,341억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 6종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -671,10 +671,10 @@
         <v>52</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>552687720</v>
+        <v>563306120</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>0.092</v>
+        <v>0.105</v>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -690,10 +690,10 @@
         <v>-49</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2560651800</v>
+        <v>-2609847800</v>
       </c>
       <c r="J6" s="16" t="n">
-        <v>-0.424</v>
+        <v>-0.489</v>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>27</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1086335550</v>
+        <v>1107206550</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>0.18</v>
+        <v>0.207</v>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -730,10 +730,10 @@
         <v>-20</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2102820000</v>
+        <v>-2143220000</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>-0.348</v>
+        <v>-0.401</v>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
@@ -751,10 +751,10 @@
         <v>11</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>531326400</v>
+        <v>541534400</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
         <v>-13</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1117825800</v>
+        <v>-1139301800</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>-0.185</v>
+        <v>-0.213</v>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1080141600</v>
+        <v>1100893600</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0.179</v>
+        <v>0.206</v>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
         <v>-13</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1795829100</v>
+        <v>-1830331100</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>-0.297</v>
+        <v>-0.343</v>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
@@ -831,10 +831,10 @@
         <v>5</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>451273500</v>
+        <v>459943500</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>0.075</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         <v>-6</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-2717010000</v>
+        <v>-2769210000</v>
       </c>
       <c r="J10" s="16" t="n">
-        <v>-0.45</v>
+        <v>-0.518</v>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
@@ -871,10 +871,10 @@
         <v>4</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1463646000</v>
+        <v>1491766000</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>0.242</v>
+        <v>0.279</v>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
         <v>-3</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-768258000</v>
+        <v>-783018000</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>-0.127</v>
+        <v>-0.147</v>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,954억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,858억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -928,7 +928,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,774억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,365억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -952,7 +952,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,898억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,838억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -976,7 +976,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 394억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 5종목  /  매도 6종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 355억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 5종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1072,10 +1072,10 @@
         <v>12</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>63516000</v>
+        <v>53952000</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.161</v>
+        <v>0.152</v>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         <v>-76</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-40226800</v>
+        <v>-40432000</v>
       </c>
       <c r="J25" s="16" t="n">
-        <v>-0.102</v>
+        <v>-0.114</v>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
@@ -1112,10 +1112,10 @@
         <v>11</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>26591400</v>
+        <v>19272000</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0.067</v>
+        <v>0.054</v>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
         <v>-32</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-46312960</v>
+        <v>-45209600</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>-0.117</v>
+        <v>-0.127</v>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
@@ -1152,10 +1152,10 @@
         <v>10</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>130824000</v>
+        <v>105280000</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>0.332</v>
+        <v>0.296</v>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
@@ -1171,10 +1171,10 @@
         <v>-23</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-72407450</v>
+        <v>-70288000</v>
       </c>
       <c r="J27" s="16" t="n">
-        <v>-0.184</v>
+        <v>-0.198</v>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
@@ -1192,10 +1192,10 @@
         <v>9</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>121367700</v>
+        <v>110952000</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>0.308</v>
+        <v>0.312</v>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
@@ -1211,10 +1211,10 @@
         <v>-17</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-75745200</v>
+        <v>-70448000</v>
       </c>
       <c r="J28" s="16" t="n">
-        <v>-0.192</v>
+        <v>-0.198</v>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
@@ -1232,10 +1232,10 @@
         <v>7</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>117789000</v>
+        <v>99568000</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>0.299</v>
+        <v>0.28</v>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         <v>-9</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-76574700</v>
+        <v>-61920000</v>
       </c>
       <c r="J29" s="16" t="n">
-        <v>-0.194</v>
+        <v>-0.174</v>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
@@ -1277,10 +1277,10 @@
         <v>-5</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-105662500</v>
+        <v>-106200000</v>
       </c>
       <c r="J30" s="16" t="n">
-        <v>-0.268</v>
+        <v>-0.299</v>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 639억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 632억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>

--- a/reports/pdf_change_20260703.xlsx
+++ b/reports/pdf_change_20260703.xlsx
@@ -763,17 +763,17 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>파두  (편출)</t>
+          <t>에코프로비엠  (편출)</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1139301800</v>
+        <v>-1830331100</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>-0.213</v>
+        <v>-0.343</v>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
@@ -803,17 +803,17 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>에코프로비엠  (편출)</t>
+          <t>파두  (편출)</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1830331100</v>
+        <v>-1139301800</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>-0.343</v>
+        <v>-0.213</v>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>

--- a/reports/pdf_change_20260703.xlsx
+++ b/reports/pdf_change_20260703.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
-    <numFmt numFmtId="165" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;;0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -158,7 +157,7 @@
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -168,7 +167,7 @@
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -575,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,341억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 6종목  /  매도 6종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      당일 2026-07-03  vs  전영업일 2026-07-02      매수 6종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,11 +669,15 @@
       <c r="B6" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>563306120</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>0.105</v>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -689,11 +692,15 @@
       <c r="H6" s="15" t="n">
         <v>-49</v>
       </c>
-      <c r="I6" s="15" t="n">
-        <v>-2609847800</v>
-      </c>
-      <c r="J6" s="16" t="n">
-        <v>-0.489</v>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -710,11 +717,15 @@
       <c r="B7" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C7" s="11" t="n">
-        <v>1107206550</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>0.207</v>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -729,11 +740,15 @@
       <c r="H7" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I7" s="15" t="n">
-        <v>-2143220000</v>
-      </c>
-      <c r="J7" s="16" t="n">
-        <v>-0.401</v>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
@@ -750,11 +765,15 @@
       <c r="B8" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>541534400</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>0.101</v>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
@@ -763,17 +782,21 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>에코프로비엠  (편출)</t>
+          <t>파두  (편출)</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I8" s="15" t="n">
-        <v>-1830331100</v>
-      </c>
-      <c r="J8" s="16" t="n">
-        <v>-0.343</v>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
@@ -790,11 +813,15 @@
       <c r="B9" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>1100893600</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>0.206</v>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
@@ -803,17 +830,21 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>파두  (편출)</t>
+          <t>에코프로비엠  (편출)</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I9" s="15" t="n">
-        <v>-1139301800</v>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>-0.213</v>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
@@ -830,11 +861,15 @@
       <c r="B10" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>459943500</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>0.08599999999999999</v>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
@@ -849,11 +884,15 @@
       <c r="H10" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I10" s="15" t="n">
-        <v>-2769210000</v>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>-0.518</v>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
@@ -870,11 +909,15 @@
       <c r="B11" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>1491766000</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>0.279</v>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
@@ -889,11 +932,15 @@
       <c r="H11" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I11" s="15" t="n">
-        <v>-783018000</v>
-      </c>
-      <c r="J11" s="16" t="n">
-        <v>-0.147</v>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
@@ -904,7 +951,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,858억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -928,7 +975,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,365억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -952,7 +999,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,838억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -976,7 +1023,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 355억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 5종목  /  매도 6종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      당일 2026-07-03  vs  전영업일 2026-07-02      매수 5종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1071,11 +1118,15 @@
       <c r="B25" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C25" s="11" t="n">
-        <v>53952000</v>
-      </c>
-      <c r="D25" s="12" t="n">
-        <v>0.152</v>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
@@ -1090,11 +1141,15 @@
       <c r="H25" s="15" t="n">
         <v>-76</v>
       </c>
-      <c r="I25" s="15" t="n">
-        <v>-40432000</v>
-      </c>
-      <c r="J25" s="16" t="n">
-        <v>-0.114</v>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
@@ -1111,11 +1166,15 @@
       <c r="B26" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C26" s="11" t="n">
-        <v>19272000</v>
-      </c>
-      <c r="D26" s="12" t="n">
-        <v>0.054</v>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
@@ -1130,11 +1189,15 @@
       <c r="H26" s="15" t="n">
         <v>-32</v>
       </c>
-      <c r="I26" s="15" t="n">
-        <v>-45209600</v>
-      </c>
-      <c r="J26" s="16" t="n">
-        <v>-0.127</v>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
@@ -1151,11 +1214,15 @@
       <c r="B27" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>105280000</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>0.296</v>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
@@ -1170,11 +1237,15 @@
       <c r="H27" s="15" t="n">
         <v>-23</v>
       </c>
-      <c r="I27" s="15" t="n">
-        <v>-70288000</v>
-      </c>
-      <c r="J27" s="16" t="n">
-        <v>-0.198</v>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
@@ -1191,11 +1262,15 @@
       <c r="B28" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C28" s="11" t="n">
-        <v>110952000</v>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>0.312</v>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
@@ -1210,11 +1285,15 @@
       <c r="H28" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="I28" s="15" t="n">
-        <v>-70448000</v>
-      </c>
-      <c r="J28" s="16" t="n">
-        <v>-0.198</v>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
@@ -1231,11 +1310,15 @@
       <c r="B29" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C29" s="11" t="n">
-        <v>99568000</v>
-      </c>
-      <c r="D29" s="12" t="n">
-        <v>0.28</v>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
@@ -1250,11 +1333,15 @@
       <c r="H29" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I29" s="15" t="n">
-        <v>-61920000</v>
-      </c>
-      <c r="J29" s="16" t="n">
-        <v>-0.174</v>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
@@ -1276,11 +1363,15 @@
       <c r="H30" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I30" s="15" t="n">
-        <v>-106200000</v>
-      </c>
-      <c r="J30" s="16" t="n">
-        <v>-0.299</v>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
@@ -1291,7 +1382,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 632억      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      당일 2026-07-03  vs  전영업일 2026-07-02      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
